--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_AOC_within_set_range.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_AOC_within_set_range.xlsx
@@ -381,641 +381,641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.3259457907318003</v>
+        <v>0.1439367068839871</v>
       </c>
       <c r="C2">
-        <v>0.5881588511097834</v>
+        <v>0.1140333333333333</v>
       </c>
       <c r="D2">
-        <v>1.146477931053171</v>
+        <v>0.5512363420084133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.3465186835785276</v>
+        <v>0.08748698363416396</v>
       </c>
       <c r="C3">
-        <v>0.40254802121745</v>
+        <v>0.110774018095175</v>
       </c>
       <c r="D3">
-        <v>0.9050482463801807</v>
+        <v>0.346895560207545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.2300676967271432</v>
+        <v>0.203713014019146</v>
       </c>
       <c r="C4">
-        <v>0.2787090400355628</v>
+        <v>0.3073405144916294</v>
       </c>
       <c r="D4">
-        <v>0.6359527668646529</v>
+        <v>0.6880956295918567</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.1794937883848571</v>
+        <v>0.01425555555555558</v>
       </c>
       <c r="C5">
-        <v>0.1856728922412866</v>
+        <v>0.101868376113963</v>
       </c>
       <c r="D5">
-        <v>0.5118238246649667</v>
+        <v>0.31887514008866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.203713014019146</v>
+        <v>0.2504599383184931</v>
       </c>
       <c r="C6">
-        <v>0.3073405144916294</v>
+        <v>0.2725518714740754</v>
       </c>
       <c r="D6">
-        <v>0.6880956295918567</v>
+        <v>0.557796059717775</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.08748698363416396</v>
+        <v>0.001855555555555499</v>
       </c>
       <c r="C7">
-        <v>0.110774018095175</v>
+        <v>0.06361519607108834</v>
       </c>
       <c r="D7">
-        <v>0.346895560207545</v>
+        <v>0.3132447787796001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.01864530012853716</v>
+        <v>0.05932690228801307</v>
       </c>
       <c r="C8">
-        <v>0.07525332405691865</v>
+        <v>0.06465854172671903</v>
       </c>
       <c r="D8">
-        <v>0.2593340696082403</v>
+        <v>0.1910905199641929</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.3317884700521478</v>
+        <v>0.000247843521153146</v>
       </c>
       <c r="C9">
-        <v>0.2846692600997245</v>
+        <v>0.127705229661096</v>
       </c>
       <c r="D9">
-        <v>1.039535212873961</v>
+        <v>0.286579970005623</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.07801704553294264</v>
+        <v>0.2803896859852618</v>
       </c>
       <c r="C10">
-        <v>0.1921183155839739</v>
+        <v>0.5150694852207556</v>
       </c>
       <c r="D10">
-        <v>0.3821300635771117</v>
+        <v>1.06133314927152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.001855555555555499</v>
+        <v>0.3259457907318003</v>
       </c>
       <c r="C11">
-        <v>0.06361519607108834</v>
+        <v>0.5881588511097834</v>
       </c>
       <c r="D11">
-        <v>0.3132447787796001</v>
+        <v>1.146477931053171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.2504599383184931</v>
+        <v>0.1656751938391031</v>
       </c>
       <c r="C12">
-        <v>0.2725518714740754</v>
+        <v>0.3879325434177008</v>
       </c>
       <c r="D12">
-        <v>0.557796059717775</v>
+        <v>0.7870540175948121</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1439367068839871</v>
+        <v>0.3160019895275373</v>
       </c>
       <c r="C13">
-        <v>0.1140333333333333</v>
+        <v>0.3388972064702279</v>
       </c>
       <c r="D13">
-        <v>0.5512363420084133</v>
+        <v>0.7738428034616354</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.01074444444444445</v>
+        <v>0.3317884700521478</v>
       </c>
       <c r="C14">
-        <v>0.5822890204186386</v>
+        <v>0.2846692600997245</v>
       </c>
       <c r="D14">
-        <v>0.9697637826594872</v>
+        <v>1.039535212873961</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15">
-        <v>4.956123468546902E-05</v>
+        <v>0.1996793597467594</v>
       </c>
       <c r="C15">
-        <v>0.3107170997808707</v>
+        <v>0.478637854946706</v>
       </c>
       <c r="D15">
-        <v>0.4845879133665592</v>
+        <v>0.7157723565301773</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16">
-        <v>-0.02812222222222216</v>
+        <v>0.3776029064267116</v>
       </c>
       <c r="C16">
-        <v>0.4532751320699412</v>
+        <v>0.4235075808222732</v>
       </c>
       <c r="D16">
-        <v>0.6854998810488302</v>
+        <v>0.713898671704049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17">
-        <v>-0.004866666666666575</v>
+        <v>0.01154444444444447</v>
       </c>
       <c r="C17">
-        <v>0.1051120846192009</v>
+        <v>0.04631169406551183</v>
       </c>
       <c r="D17">
-        <v>0.6158304517968303</v>
+        <v>0.2115695758459479</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.2803896859852618</v>
+        <v>0.3197399752123996</v>
       </c>
       <c r="C18">
-        <v>0.5150694852207556</v>
+        <v>0.4548533952777232</v>
       </c>
       <c r="D18">
-        <v>1.06133314927152</v>
+        <v>0.9190863717643822</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.4222264700402206</v>
+        <v>0.07801704553294264</v>
       </c>
       <c r="C19">
-        <v>0.5375802857724237</v>
+        <v>0.1921183155839739</v>
       </c>
       <c r="D19">
-        <v>1.451877140938295</v>
+        <v>0.3821300635771117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.44408739857069</v>
+        <v>0.2300676967271432</v>
       </c>
       <c r="C20">
-        <v>0.5223340840634582</v>
+        <v>0.2787090400355628</v>
       </c>
       <c r="D20">
-        <v>0.9585221957357458</v>
+        <v>0.6359527668646529</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.5625108842442919</v>
+        <v>-0.004866666666666575</v>
       </c>
       <c r="C21">
-        <v>0.676277891833526</v>
+        <v>0.1051120846192009</v>
       </c>
       <c r="D21">
-        <v>1.370400752648951</v>
+        <v>0.6158304517968303</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.1656751938391031</v>
+        <v>0.06301348211134705</v>
       </c>
       <c r="C22">
-        <v>0.3879325434177008</v>
+        <v>0.09179151144454534</v>
       </c>
       <c r="D22">
-        <v>0.7870540175948121</v>
+        <v>0.3302443440556934</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.05932690228801307</v>
+        <v>0.03126186256346208</v>
       </c>
       <c r="C23">
-        <v>0.06465854172671903</v>
+        <v>0.04717956354912567</v>
       </c>
       <c r="D23">
-        <v>0.1910905199641929</v>
+        <v>0.1573109422458929</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.0505549203483957</v>
+        <v>0.1794937883848571</v>
       </c>
       <c r="C24">
-        <v>0.3904576970798735</v>
+        <v>0.1856728922412866</v>
       </c>
       <c r="D24">
-        <v>0.6164099426624308</v>
+        <v>0.5118238246649667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.4842019950769823</v>
+        <v>0.2510928808891331</v>
       </c>
       <c r="C25">
-        <v>0.5820965258351068</v>
+        <v>0.3942661619164919</v>
       </c>
       <c r="D25">
-        <v>0.8774741716407291</v>
+        <v>0.8897765658427196</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.2510928808891331</v>
+        <v>4.956123468546902E-05</v>
       </c>
       <c r="C26">
-        <v>0.3942661619164919</v>
+        <v>0.3107170997808707</v>
       </c>
       <c r="D26">
-        <v>0.8897765658427196</v>
+        <v>0.4845879133665592</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.286778743850914</v>
+        <v>0.4859754250572782</v>
       </c>
       <c r="C27">
-        <v>0.5611378047251726</v>
+        <v>0.7416476946837185</v>
       </c>
       <c r="D27">
-        <v>1.008241443488145</v>
+        <v>1.284113643949408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.06301348211134705</v>
+        <v>0.01864530012853716</v>
       </c>
       <c r="C28">
-        <v>0.09179151144454534</v>
+        <v>0.07525332405691865</v>
       </c>
       <c r="D28">
-        <v>0.3302443440556934</v>
+        <v>0.2593340696082403</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.03126186256346208</v>
+        <v>0.5109292081420658</v>
       </c>
       <c r="C29">
-        <v>0.04717956354912567</v>
+        <v>0.4973202735137644</v>
       </c>
       <c r="D29">
-        <v>0.1573109422458929</v>
+        <v>1.071234815818449</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.3160019895275373</v>
+        <v>0.4222264700402206</v>
       </c>
       <c r="C30">
-        <v>0.3388972064702279</v>
+        <v>0.5375802857724237</v>
       </c>
       <c r="D30">
-        <v>0.7738428034616354</v>
+        <v>1.451877140938295</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.3776029064267116</v>
+        <v>0.01074444444444445</v>
       </c>
       <c r="C31">
-        <v>0.4235075808222732</v>
+        <v>0.5822890204186386</v>
       </c>
       <c r="D31">
-        <v>0.713898671704049</v>
+        <v>0.9697637826594872</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.4859754250572782</v>
+        <v>0.5625108842442919</v>
       </c>
       <c r="C32">
-        <v>0.7416476946837185</v>
+        <v>0.676277891833526</v>
       </c>
       <c r="D32">
-        <v>1.284113643949408</v>
+        <v>1.370400752648951</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.3177538097812108</v>
+        <v>0.3465186835785276</v>
       </c>
       <c r="C33">
-        <v>0.4078867939210875</v>
+        <v>0.40254802121745</v>
       </c>
       <c r="D33">
-        <v>0.7419943577279704</v>
+        <v>0.9050482463801807</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.5109292081420658</v>
+        <v>0.3177538097812108</v>
       </c>
       <c r="C34">
-        <v>0.4973202735137644</v>
+        <v>0.4078867939210875</v>
       </c>
       <c r="D34">
-        <v>1.071234815818449</v>
+        <v>0.7419943577279704</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.01154444444444447</v>
+        <v>-0.02812222222222216</v>
       </c>
       <c r="C35">
-        <v>0.04631169406551183</v>
+        <v>0.4532751320699412</v>
       </c>
       <c r="D35">
-        <v>0.2115695758459479</v>
+        <v>0.6854998810488302</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.2704771926711415</v>
+        <v>0.08487419602634849</v>
       </c>
       <c r="C36">
-        <v>0.3849447275234898</v>
+        <v>0.1733088468756599</v>
       </c>
       <c r="D36">
-        <v>0.7673612563095145</v>
+        <v>0.53397339348739</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.08487419602634849</v>
+        <v>0.0505549203483957</v>
       </c>
       <c r="C37">
-        <v>0.1733088468756599</v>
+        <v>0.3904576970798735</v>
       </c>
       <c r="D37">
-        <v>0.53397339348739</v>
+        <v>0.6164099426624308</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.1996793597467594</v>
+        <v>0.2704771926711415</v>
       </c>
       <c r="C38">
-        <v>0.478637854946706</v>
+        <v>0.3849447275234898</v>
       </c>
       <c r="D38">
-        <v>0.7157723565301773</v>
+        <v>0.7673612563095145</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.01425555555555558</v>
+        <v>0.44408739857069</v>
       </c>
       <c r="C39">
-        <v>0.101868376113963</v>
+        <v>0.5223340840634582</v>
       </c>
       <c r="D39">
-        <v>0.31887514008866</v>
+        <v>0.9585221957357458</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.3197399752123996</v>
+        <v>0.4842019950769823</v>
       </c>
       <c r="C40">
-        <v>0.4548533952777232</v>
+        <v>0.5820965258351068</v>
       </c>
       <c r="D40">
-        <v>0.9190863717643822</v>
+        <v>0.8774741716407291</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.000247843521153146</v>
+        <v>0.286778743850914</v>
       </c>
       <c r="C41">
-        <v>0.127705229661096</v>
+        <v>0.5611378047251726</v>
       </c>
       <c r="D41">
-        <v>0.286579970005623</v>
+        <v>1.008241443488145</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1043,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
